--- a/Backtest/01-12-17/NASDAQstock_01-12-17period252RS90.xlsx
+++ b/Backtest/01-12-17/NASDAQstock_01-12-17period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Backtest/01-12-17/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E4571B-2A28-D44B-8DF3-FEA86815CB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -484,12 +490,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -497,8 +503,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -544,17 +557,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -592,7 +613,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -626,6 +647,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -660,9 +682,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -835,9 +858,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
@@ -957,34 +980,34 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>93.85898407884761</v>
+        <v>93.858984078847612</v>
       </c>
       <c r="C2">
         <v>1390</v>
       </c>
       <c r="D2">
-        <v>32.37</v>
+        <v>32.369999999999997</v>
       </c>
       <c r="E2">
         <v>1.72</v>
       </c>
       <c r="F2">
-        <v>-0.4361460525631877</v>
+        <v>-0.43614605256318772</v>
       </c>
       <c r="G2">
         <v>1.82</v>
       </c>
       <c r="H2">
-        <v>-0.245889583322052</v>
+        <v>-0.24588958332205199</v>
       </c>
       <c r="I2">
-        <v>32.05199966430664</v>
+        <v>32.051999664306642</v>
       </c>
       <c r="J2">
         <v>31.26200008392334</v>
       </c>
       <c r="K2">
-        <v>28.81499996185303</v>
+        <v>28.814999961853029</v>
       </c>
       <c r="L2">
         <v>22.78239996910095</v>
@@ -993,7 +1016,7 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P2">
         <v>15</v>
@@ -1008,7 +1031,7 @@
         <v>2</v>
       </c>
       <c r="T2">
-        <v>18.33333333333333</v>
+        <v>18.333333333333329</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -1020,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>16.74</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="Y2">
         <v>33.14</v>
@@ -1059,7 +1082,7 @@
         <v>122</v>
       </c>
       <c r="AK2">
-        <v>67.79802165245819</v>
+        <v>67.798021652458189</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1067,7 +1090,7 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.58832448824867</v>
+        <v>96.588324488248674</v>
       </c>
       <c r="C3">
         <v>886</v>
@@ -1079,7 +1102,7 @@
         <v>0.96</v>
       </c>
       <c r="F3">
-        <v>-1.097618114543721</v>
+        <v>-1.0976181145437209</v>
       </c>
       <c r="G3">
         <v>1.38</v>
@@ -1091,19 +1114,19 @@
         <v>28.32200012207031</v>
       </c>
       <c r="J3">
-        <v>27.39399995803833</v>
+        <v>27.393999958038329</v>
       </c>
       <c r="K3">
-        <v>25.46559986114502</v>
+        <v>25.465599861145019</v>
       </c>
       <c r="L3">
-        <v>20.96064994812012</v>
+        <v>20.960649948120121</v>
       </c>
       <c r="M3">
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1169,7 +1192,7 @@
         <v>123</v>
       </c>
       <c r="AK3">
-        <v>60.20862544822334</v>
+        <v>60.208625448223337</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,7 +1200,7 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>99.59565327268133</v>
+        <v>99.595653272681332</v>
       </c>
       <c r="C4">
         <v>356</v>
@@ -1186,10 +1209,10 @@
         <v>53.34</v>
       </c>
       <c r="E4">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="F4">
-        <v>2.105299238204123</v>
+        <v>2.1052992382041231</v>
       </c>
       <c r="G4">
         <v>3.67</v>
@@ -1201,13 +1224,13 @@
         <v>53.1120002746582</v>
       </c>
       <c r="J4">
-        <v>42.16700019836426</v>
+        <v>42.167000198364263</v>
       </c>
       <c r="K4">
         <v>31.1260001373291</v>
       </c>
       <c r="L4">
-        <v>22.31795010566712</v>
+        <v>22.317950105667119</v>
       </c>
       <c r="M4">
         <v>1.26</v>
@@ -1228,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>15.55555555555556</v>
+        <v>15.555555555555561</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1279,7 +1302,7 @@
         <v>124</v>
       </c>
       <c r="AK4">
-        <v>55.56204985579867</v>
+        <v>55.562049855798669</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1287,7 +1310,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>90.21986353297953</v>
+        <v>90.219863532979531</v>
       </c>
       <c r="C5">
         <v>1848</v>
@@ -1299,13 +1322,13 @@
         <v>0.9</v>
       </c>
       <c r="F5">
-        <v>-1.149839593121131</v>
+        <v>-1.1498395931211309</v>
       </c>
       <c r="G5">
         <v>1.05</v>
       </c>
       <c r="H5">
-        <v>-1.22408407954583</v>
+        <v>-1.2240840795458301</v>
       </c>
       <c r="I5">
         <v>130.9840026855469</v>
@@ -1317,7 +1340,7 @@
         <v>126.3586003112793</v>
       </c>
       <c r="L5">
-        <v>109.0564002227783</v>
+        <v>109.05640022277829</v>
       </c>
       <c r="M5">
         <v>1.02</v>
@@ -1397,7 +1420,7 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>96.73995451099317</v>
+        <v>96.739954510993172</v>
       </c>
       <c r="C6">
         <v>1239</v>
@@ -1409,22 +1432,22 @@
         <v>1.74</v>
       </c>
       <c r="F6">
-        <v>-0.4187388930373842</v>
+        <v>-0.41873889303738421</v>
       </c>
       <c r="G6">
         <v>1.62</v>
       </c>
       <c r="H6">
-        <v>-0.4999660758477085</v>
+        <v>-0.49996607584770852</v>
       </c>
       <c r="I6">
-        <v>28.25999984741211</v>
+        <v>28.259999847412111</v>
       </c>
       <c r="J6">
-        <v>27.42849979400635</v>
+        <v>27.428499794006349</v>
       </c>
       <c r="K6">
-        <v>25.90799991607666</v>
+        <v>25.907999916076658</v>
       </c>
       <c r="L6">
         <v>20.09449996471405</v>
@@ -1433,7 +1456,7 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1499,7 +1522,7 @@
         <v>126</v>
       </c>
       <c r="AK6">
-        <v>53.29933243340459</v>
+        <v>53.299332433404587</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,7 +1530,7 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>92.26686884003033</v>
+        <v>92.266868840030327</v>
       </c>
       <c r="C7">
         <v>293</v>
@@ -1519,31 +1542,31 @@
         <v>1.58</v>
       </c>
       <c r="F7">
-        <v>-0.5579961692438121</v>
+        <v>-0.55799616924381212</v>
       </c>
       <c r="G7">
         <v>1.44</v>
       </c>
       <c r="H7">
-        <v>-0.7286349191207996</v>
+        <v>-0.72863491912079958</v>
       </c>
       <c r="I7">
-        <v>26.80713882446289</v>
+        <v>26.807138824462889</v>
       </c>
       <c r="J7">
-        <v>25.91397104263306</v>
+        <v>25.913971042633062</v>
       </c>
       <c r="K7">
-        <v>24.30260280609131</v>
+        <v>24.302602806091311</v>
       </c>
       <c r="L7">
-        <v>20.45428599834442</v>
+        <v>20.454285998344421</v>
       </c>
       <c r="M7">
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1558,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1585,7 +1608,7 @@
         <v>2820</v>
       </c>
       <c r="AC7">
-        <v>88.45999999999999</v>
+        <v>88.46</v>
       </c>
       <c r="AD7">
         <v>1.94</v>
@@ -1594,7 +1617,7 @@
         <v>13.95</v>
       </c>
       <c r="AF7">
-        <v>138.89</v>
+        <v>138.88999999999999</v>
       </c>
       <c r="AG7">
         <v>-30.77</v>
@@ -1609,7 +1632,7 @@
         <v>127</v>
       </c>
       <c r="AK7">
-        <v>51.87702518637499</v>
+        <v>51.877025186374993</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,7 +1640,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>97.29593126105635</v>
+        <v>97.295931261056353</v>
       </c>
       <c r="C8">
         <v>826</v>
@@ -1629,31 +1652,31 @@
         <v>2.1</v>
       </c>
       <c r="F8">
-        <v>-0.1054100215729211</v>
+        <v>-0.10541002157292111</v>
       </c>
       <c r="G8">
         <v>1.53</v>
       </c>
       <c r="H8">
-        <v>-0.6143004974842541</v>
+        <v>-0.61430049748425408</v>
       </c>
       <c r="I8">
-        <v>232.6639984130859</v>
+        <v>232.66399841308589</v>
       </c>
       <c r="J8">
-        <v>229.9389991760254</v>
+        <v>229.93899917602539</v>
       </c>
       <c r="K8">
-        <v>210.1220001220703</v>
+        <v>210.12200012207029</v>
       </c>
       <c r="L8">
-        <v>159.5442500686646</v>
+        <v>159.54425006866461</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P8">
         <v>13</v>
@@ -1686,7 +1709,7 @@
         <v>248.23</v>
       </c>
       <c r="Z8">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="AA8">
         <v>11.12</v>
@@ -1719,7 +1742,7 @@
         <v>128</v>
       </c>
       <c r="AK8">
-        <v>51.36182187569411</v>
+        <v>51.361821875694112</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1739,13 +1762,13 @@
         <v>1.69</v>
       </c>
       <c r="F9">
-        <v>-0.4622567918518929</v>
+        <v>-0.46225679185189289</v>
       </c>
       <c r="G9">
         <v>1.32</v>
       </c>
       <c r="H9">
-        <v>-0.8810808146361934</v>
+        <v>-0.88108081463619337</v>
       </c>
       <c r="I9">
         <v>16.28800029754639</v>
@@ -1754,7 +1777,7 @@
         <v>15.23550019264221</v>
       </c>
       <c r="K9">
-        <v>15.01860004425049</v>
+        <v>15.018600044250491</v>
       </c>
       <c r="L9">
         <v>13.59314998626709</v>
@@ -1793,10 +1816,10 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="Z9">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AA9">
         <v>0.15</v>
@@ -1808,10 +1831,10 @@
         <v>2893.07</v>
       </c>
       <c r="AD9">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AE9">
-        <v>133.14</v>
+        <v>133.13999999999999</v>
       </c>
       <c r="AF9">
         <v>-56.33</v>
@@ -1829,7 +1852,7 @@
         <v>129</v>
       </c>
       <c r="AK9">
-        <v>46.91066117271669</v>
+        <v>46.910661172716686</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1837,7 +1860,7 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>94.69294920394238</v>
+        <v>94.692949203942376</v>
       </c>
       <c r="C10">
         <v>1340</v>
@@ -1849,31 +1872,31 @@
         <v>1.42</v>
       </c>
       <c r="F10">
-        <v>-0.6972534454502402</v>
+        <v>-0.69725344545024015</v>
       </c>
       <c r="G10">
         <v>1.54</v>
       </c>
       <c r="H10">
-        <v>-0.6015966728579712</v>
+        <v>-0.60159667285797125</v>
       </c>
       <c r="I10">
-        <v>87.59999999999999</v>
+        <v>87.6</v>
       </c>
       <c r="J10">
-        <v>83.96250000000001</v>
+        <v>83.962500000000006</v>
       </c>
       <c r="K10">
-        <v>77.52160018920898</v>
+        <v>77.521600189208982</v>
       </c>
       <c r="L10">
-        <v>62.54727499008179</v>
+        <v>62.547274990081789</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="O10" t="s">
         <v>82</v>
@@ -1906,7 +1929,7 @@
         <v>44.56</v>
       </c>
       <c r="Y10">
-        <v>88.48999999999999</v>
+        <v>88.49</v>
       </c>
       <c r="Z10">
         <v>3.4</v>
@@ -1930,7 +1953,7 @@
         <v>330.43</v>
       </c>
       <c r="AG10">
-        <v>137.7</v>
+        <v>137.69999999999999</v>
       </c>
       <c r="AH10" t="s">
         <v>92</v>
@@ -1942,7 +1965,7 @@
         <v>130</v>
       </c>
       <c r="AK10">
-        <v>46.21113015991543</v>
+        <v>46.211130159915427</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1950,7 +1973,7 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>97.72554965883245</v>
+        <v>97.725549658832449</v>
       </c>
       <c r="C11">
         <v>1443</v>
@@ -1962,31 +1985,31 @@
         <v>3.79</v>
       </c>
       <c r="F11">
-        <v>1.365494958357475</v>
+        <v>1.3654949583574749</v>
       </c>
       <c r="G11">
         <v>2.39</v>
       </c>
       <c r="H11">
-        <v>0.4782284203760693</v>
+        <v>0.47822842037606927</v>
       </c>
       <c r="I11">
-        <v>61.9979995727539</v>
+        <v>61.997999572753898</v>
       </c>
       <c r="J11">
-        <v>61.70100002288818</v>
+        <v>61.701000022888181</v>
       </c>
       <c r="K11">
-        <v>56.65559989929199</v>
+        <v>56.655599899291992</v>
       </c>
       <c r="L11">
-        <v>42.68250001907349</v>
+        <v>42.682500019073487</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2052,7 +2075,7 @@
         <v>131</v>
       </c>
       <c r="AK11">
-        <v>40.96450091399256</v>
+        <v>40.964500913992559</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2060,34 +2083,34 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>96.36087945413192</v>
+        <v>96.360879454131918</v>
       </c>
       <c r="C12">
         <v>1569</v>
       </c>
       <c r="D12">
-        <v>69.84999999999999</v>
+        <v>69.849999999999994</v>
       </c>
       <c r="E12">
         <v>2.33</v>
       </c>
       <c r="F12">
-        <v>0.09477231297381919</v>
+        <v>9.4772312973819189E-2</v>
       </c>
       <c r="G12">
         <v>1.8</v>
       </c>
       <c r="H12">
-        <v>-0.2712972325746177</v>
+        <v>-0.27129723257461769</v>
       </c>
       <c r="I12">
-        <v>69.42799987792969</v>
+        <v>69.427999877929693</v>
       </c>
       <c r="J12">
-        <v>65.58000030517579</v>
+        <v>65.580000305175787</v>
       </c>
       <c r="K12">
-        <v>58.24220024108887</v>
+        <v>58.242200241088867</v>
       </c>
       <c r="L12">
         <v>42.40784999847412</v>
@@ -2111,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="T12">
-        <v>16.66666666666666</v>
+        <v>16.666666666666661</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -2126,7 +2149,7 @@
         <v>26.82</v>
       </c>
       <c r="Y12">
-        <v>71.23999999999999</v>
+        <v>71.239999999999995</v>
       </c>
       <c r="Z12">
         <v>1.17</v>
@@ -2138,7 +2161,7 @@
         <v>6.59</v>
       </c>
       <c r="AC12">
-        <v>40.91</v>
+        <v>40.909999999999997</v>
       </c>
       <c r="AD12">
         <v>7.54</v>
@@ -2162,7 +2185,7 @@
         <v>132</v>
       </c>
       <c r="AK12">
-        <v>40.82384255071769</v>
+        <v>40.823842550717693</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2170,7 +2193,7 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>96.63886782916352</v>
+        <v>96.638867829163516</v>
       </c>
       <c r="C13">
         <v>226</v>
@@ -2182,7 +2205,7 @@
         <v>2.58</v>
       </c>
       <c r="F13">
-        <v>0.312361807046363</v>
+        <v>0.31236180704636302</v>
       </c>
       <c r="G13">
         <v>2.36</v>
@@ -2197,7 +2220,7 @@
         <v>23.91100015640259</v>
       </c>
       <c r="K13">
-        <v>21.89800006866455</v>
+        <v>21.898000068664551</v>
       </c>
       <c r="L13">
         <v>17.61170006752014</v>
@@ -2272,7 +2295,7 @@
         <v>133</v>
       </c>
       <c r="AK13">
-        <v>39.46922766485702</v>
+        <v>39.469227664857023</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2280,7 +2303,7 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>92.2163254991155</v>
+        <v>92.216325499115499</v>
       </c>
       <c r="C14">
         <v>1029</v>
@@ -2292,7 +2315,7 @@
         <v>1.5</v>
       </c>
       <c r="F14">
-        <v>-0.6276248073470262</v>
+        <v>-0.62762480734702619</v>
       </c>
       <c r="G14">
         <v>1.31</v>
@@ -2301,16 +2324,16 @@
         <v>-0.8937846392624762</v>
       </c>
       <c r="I14">
-        <v>38.43000030517578</v>
+        <v>38.430000305175781</v>
       </c>
       <c r="J14">
-        <v>37.01749973297119</v>
+        <v>37.017499732971189</v>
       </c>
       <c r="K14">
-        <v>35.81100006103516</v>
+        <v>35.811000061035159</v>
       </c>
       <c r="L14">
-        <v>30.77200001716614</v>
+        <v>30.772000017166139</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -2346,7 +2369,7 @@
         <v>22.03</v>
       </c>
       <c r="Y14">
-        <v>39.45</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="Z14">
         <v>1.37</v>
@@ -2382,7 +2405,7 @@
         <v>134</v>
       </c>
       <c r="AK14">
-        <v>38.52307765075905</v>
+        <v>38.523077650759049</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2390,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>90.67475360121304</v>
+        <v>90.674753601213041</v>
       </c>
       <c r="C15">
         <v>799</v>
@@ -2402,25 +2425,25 @@
         <v>1.33</v>
       </c>
       <c r="F15">
-        <v>-0.7755856633163558</v>
+        <v>-0.77558566331635581</v>
       </c>
       <c r="G15">
         <v>1.24</v>
       </c>
       <c r="H15">
-        <v>-0.9827114116464561</v>
+        <v>-0.98271141164645615</v>
       </c>
       <c r="I15">
-        <v>81.50043487548828</v>
+        <v>81.500434875488281</v>
       </c>
       <c r="J15">
         <v>80.8842155456543</v>
       </c>
       <c r="K15">
-        <v>79.99132720947266</v>
+        <v>79.991327209472658</v>
       </c>
       <c r="L15">
-        <v>68.43243698120118</v>
+        <v>68.432436981201178</v>
       </c>
       <c r="M15">
         <v>1.01</v>
@@ -2492,7 +2515,7 @@
         <v>135</v>
       </c>
       <c r="AK15">
-        <v>36.91952415957168</v>
+        <v>36.919524159571679</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2500,7 +2523,7 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>90.9021986353298</v>
+        <v>90.902198635329796</v>
       </c>
       <c r="C16">
         <v>646</v>
@@ -2512,31 +2535,31 @@
         <v>3.26</v>
       </c>
       <c r="F16">
-        <v>0.9042052309236817</v>
+        <v>0.90420523092368166</v>
       </c>
       <c r="G16">
         <v>2.42</v>
       </c>
       <c r="H16">
-        <v>0.5163398942549176</v>
+        <v>0.51633989425491755</v>
       </c>
       <c r="I16">
-        <v>29.59799995422363</v>
+        <v>29.597999954223631</v>
       </c>
       <c r="J16">
-        <v>29.01749982833862</v>
+        <v>29.017499828338622</v>
       </c>
       <c r="K16">
-        <v>26.7439998626709</v>
+        <v>26.743999862670901</v>
       </c>
       <c r="L16">
-        <v>20.57282492637634</v>
+        <v>20.572824926376342</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2566,7 +2589,7 @@
         <v>15.42</v>
       </c>
       <c r="Y16">
-        <v>32.87</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="Z16">
         <v>2.02</v>
@@ -2602,7 +2625,7 @@
         <v>136</v>
       </c>
       <c r="AK16">
-        <v>36.70500539578918</v>
+        <v>36.705005395789179</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2610,43 +2633,43 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>91.18018701036138</v>
+        <v>91.180187010361379</v>
       </c>
       <c r="C17">
         <v>2037</v>
       </c>
       <c r="D17">
-        <v>68.65000000000001</v>
+        <v>68.650000000000006</v>
       </c>
       <c r="E17">
         <v>1.48</v>
       </c>
       <c r="F17">
-        <v>-0.6450319668728297</v>
+        <v>-0.64503196687282971</v>
       </c>
       <c r="G17">
         <v>1.42</v>
       </c>
       <c r="H17">
-        <v>-0.7540425683733653</v>
+        <v>-0.75404256837336525</v>
       </c>
       <c r="I17">
-        <v>69.33000030517579</v>
+        <v>69.330000305175787</v>
       </c>
       <c r="J17">
-        <v>67.46000022888184</v>
+        <v>67.460000228881839</v>
       </c>
       <c r="K17">
-        <v>61.30500007629394</v>
+        <v>61.305000076293943</v>
       </c>
       <c r="L17">
-        <v>46.67849998474121</v>
+        <v>46.678499984741208</v>
       </c>
       <c r="M17">
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2661,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U17" t="b">
         <v>1</v>
@@ -2691,7 +2714,7 @@
         <v>50.82</v>
       </c>
       <c r="AD17">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AE17">
         <v>29.58</v>
@@ -2712,7 +2735,7 @@
         <v>137</v>
       </c>
       <c r="AK17">
-        <v>35.40482257013583</v>
+        <v>35.404822570135828</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2720,7 +2743,7 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>98.6606014657569</v>
+        <v>98.660601465756898</v>
       </c>
       <c r="C18">
         <v>490</v>
@@ -2747,10 +2770,10 @@
         <v>12.55000009536743</v>
       </c>
       <c r="K18">
-        <v>12.18540006637573</v>
+        <v>12.185400066375729</v>
       </c>
       <c r="L18">
-        <v>9.699950020313263</v>
+        <v>9.6999500203132634</v>
       </c>
       <c r="M18">
         <v>1.05</v>
@@ -2822,7 +2845,7 @@
         <v>138</v>
       </c>
       <c r="AK18">
-        <v>33.35877467923397</v>
+        <v>33.358774679233967</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2830,7 +2853,7 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>91.45817538539298</v>
+        <v>91.458175385392977</v>
       </c>
       <c r="C19">
         <v>394</v>
@@ -2842,22 +2865,22 @@
         <v>2.69</v>
       </c>
       <c r="F19">
-        <v>0.4081011844382821</v>
+        <v>0.40810118443828208</v>
       </c>
       <c r="G19">
         <v>3.59</v>
       </c>
       <c r="H19">
-        <v>2.002687375530008</v>
+        <v>2.0026873755300079</v>
       </c>
       <c r="I19">
-        <v>26.93800010681152</v>
+        <v>26.938000106811518</v>
       </c>
       <c r="J19">
-        <v>26.2354998588562</v>
+        <v>26.235499858856201</v>
       </c>
       <c r="K19">
-        <v>25.84839988708496</v>
+        <v>25.848399887084959</v>
       </c>
       <c r="L19">
         <v>24.07054997444153</v>
@@ -2881,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -2908,10 +2931,10 @@
         <v>229.55</v>
       </c>
       <c r="AC19">
-        <v>64.70999999999999</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="AD19">
-        <v>34.09</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="AE19">
         <v>366.67</v>
@@ -2920,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>-64.70999999999999</v>
+        <v>-64.709999999999994</v>
       </c>
       <c r="AH19" t="s">
         <v>96</v>
@@ -2932,7 +2955,7 @@
         <v>124</v>
       </c>
       <c r="AK19">
-        <v>32.55750668794771</v>
+        <v>32.557506687947708</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2940,7 +2963,7 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>90.27040687389436</v>
+        <v>90.270406873894359</v>
       </c>
       <c r="C20">
         <v>1261</v>
@@ -2952,25 +2975,25 @@
         <v>2.02</v>
       </c>
       <c r="F20">
-        <v>-0.1750386596761351</v>
+        <v>-0.17503865967613511</v>
       </c>
       <c r="G20">
         <v>2.4</v>
       </c>
       <c r="H20">
-        <v>0.4909322450023519</v>
+        <v>0.49093224500235189</v>
       </c>
       <c r="I20">
-        <v>39.50199966430664</v>
+        <v>39.501999664306638</v>
       </c>
       <c r="J20">
-        <v>39.53249988555908</v>
+        <v>39.532499885559083</v>
       </c>
       <c r="K20">
-        <v>37.79060020446777</v>
+        <v>37.790600204467772</v>
       </c>
       <c r="L20">
-        <v>28.52325012207031</v>
+        <v>28.523250122070309</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -3018,7 +3041,7 @@
         <v>82.27</v>
       </c>
       <c r="AC20">
-        <v>128.42</v>
+        <v>128.41999999999999</v>
       </c>
       <c r="AD20">
         <v>1.54</v>
@@ -3042,7 +3065,7 @@
         <v>139</v>
       </c>
       <c r="AK20">
-        <v>32.42531238335177</v>
+        <v>32.425312383351773</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3050,7 +3073,7 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>90.72529694212787</v>
+        <v>90.725296942127869</v>
       </c>
       <c r="C21">
         <v>14</v>
@@ -3059,7 +3082,7 @@
         <v>27.16</v>
       </c>
       <c r="E21">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F21">
         <v>-0.14892792038743</v>
@@ -3068,19 +3091,19 @@
         <v>1.55</v>
       </c>
       <c r="H21">
-        <v>-0.5888928482316884</v>
+        <v>-0.58889284823168841</v>
       </c>
       <c r="I21">
-        <v>27.66040000915527</v>
+        <v>27.660400009155271</v>
       </c>
       <c r="J21">
-        <v>27.27775020599365</v>
+        <v>27.277750205993652</v>
       </c>
       <c r="K21">
-        <v>25.68940021514893</v>
+        <v>25.689400215148929</v>
       </c>
       <c r="L21">
-        <v>24.07367504119873</v>
+        <v>24.073675041198729</v>
       </c>
       <c r="M21">
         <v>1.01</v>
@@ -3113,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="Y21">
         <v>28.57</v>
@@ -3131,7 +3154,7 @@
         <v>150.43</v>
       </c>
       <c r="AD21">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="AE21">
         <v>8.26</v>
@@ -3160,7 +3183,7 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>91.30654536264848</v>
+        <v>91.306545362648478</v>
       </c>
       <c r="C22">
         <v>978</v>
@@ -3178,16 +3201,16 @@
         <v>2.71</v>
       </c>
       <c r="H22">
-        <v>0.8847508084171196</v>
+        <v>0.88475080841711962</v>
       </c>
       <c r="I22">
         <v>26.72599983215332</v>
       </c>
       <c r="J22">
-        <v>25.18949995040894</v>
+        <v>25.189499950408941</v>
       </c>
       <c r="K22">
-        <v>22.46019989013672</v>
+        <v>22.460199890136721</v>
       </c>
       <c r="L22">
         <v>19.9189757053046</v>
@@ -3262,7 +3285,7 @@
         <v>140</v>
       </c>
       <c r="AK22">
-        <v>31.54889135481928</v>
+        <v>31.548891354819279</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3270,7 +3293,7 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>93.70735405610311</v>
+        <v>93.707354056103114</v>
       </c>
       <c r="C23">
         <v>1577</v>
@@ -3282,25 +3305,25 @@
         <v>1.77</v>
       </c>
       <c r="F23">
-        <v>-0.3926281537486789</v>
+        <v>-0.39262815374867888</v>
       </c>
       <c r="G23">
         <v>1.65</v>
       </c>
       <c r="H23">
-        <v>-0.4618546019688602</v>
+        <v>-0.46185460196886019</v>
       </c>
       <c r="I23">
-        <v>59.32000045776367</v>
+        <v>59.320000457763669</v>
       </c>
       <c r="J23">
-        <v>58.59750003814698</v>
+        <v>58.597500038146983</v>
       </c>
       <c r="K23">
-        <v>54.79900016784668</v>
+        <v>54.799000167846678</v>
       </c>
       <c r="L23">
-        <v>44.58025005340576</v>
+        <v>44.580250053405763</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -3372,7 +3395,7 @@
         <v>141</v>
       </c>
       <c r="AK23">
-        <v>30.77314898325164</v>
+        <v>30.773148983251641</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3380,7 +3403,7 @@
         <v>59</v>
       </c>
       <c r="B24">
-        <v>95.98180439727066</v>
+        <v>95.981804397270665</v>
       </c>
       <c r="C24">
         <v>953</v>
@@ -3389,10 +3412,10 @@
         <v>37.28</v>
       </c>
       <c r="E24">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F24">
-        <v>0.03384725463350668</v>
+        <v>3.3847254633506678E-2</v>
       </c>
       <c r="G24">
         <v>1.87</v>
@@ -3401,13 +3424,13 @@
         <v>-0.1823704601906378</v>
       </c>
       <c r="I24">
-        <v>36.31199951171875</v>
+        <v>36.311999511718753</v>
       </c>
       <c r="J24">
-        <v>34.48699970245362</v>
+        <v>34.486999702453623</v>
       </c>
       <c r="K24">
-        <v>31.69699993133545</v>
+        <v>31.696999931335451</v>
       </c>
       <c r="L24">
         <v>26.04845003128052</v>
@@ -3416,7 +3439,7 @@
         <v>1.05</v>
       </c>
       <c r="N24">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="O24" t="s">
         <v>83</v>
@@ -3434,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
@@ -3449,7 +3472,7 @@
         <v>17.45</v>
       </c>
       <c r="Y24">
-        <v>37.38</v>
+        <v>37.380000000000003</v>
       </c>
       <c r="Z24">
         <v>7.07</v>
@@ -3485,7 +3508,7 @@
         <v>129</v>
       </c>
       <c r="AK24">
-        <v>30.72534879925252</v>
+        <v>30.725348799252519</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3493,7 +3516,7 @@
         <v>60</v>
       </c>
       <c r="B25">
-        <v>97.11902956785443</v>
+        <v>97.119029567854426</v>
       </c>
       <c r="C25">
         <v>222</v>
@@ -3511,25 +3534,25 @@
         <v>1.46</v>
       </c>
       <c r="H25">
-        <v>-0.7032272698682339</v>
+        <v>-0.70322726986823392</v>
       </c>
       <c r="I25">
-        <v>69.99600067138672</v>
+        <v>69.996000671386724</v>
       </c>
       <c r="J25">
-        <v>69.37650032043457</v>
+        <v>69.376500320434573</v>
       </c>
       <c r="K25">
-        <v>63.22670013427734</v>
+        <v>63.226700134277337</v>
       </c>
       <c r="L25">
-        <v>50.11190004348755</v>
+        <v>50.111900043487552</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -3544,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3559,10 +3582,10 @@
         <v>28.71</v>
       </c>
       <c r="Y25">
-        <v>72.98999999999999</v>
+        <v>72.989999999999995</v>
       </c>
       <c r="Z25">
-        <v>9.890000000000001</v>
+        <v>9.89</v>
       </c>
       <c r="AA25">
         <v>107.05</v>
@@ -3574,10 +3597,10 @@
         <v>218.92</v>
       </c>
       <c r="AD25">
-        <v>9.039999999999999</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="AE25">
-        <v>78.79000000000001</v>
+        <v>78.790000000000006</v>
       </c>
       <c r="AF25">
         <v>26.92</v>
@@ -3595,7 +3618,7 @@
         <v>142</v>
       </c>
       <c r="AK25">
-        <v>30.00436040197547</v>
+        <v>30.004360401975472</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3603,7 +3626,7 @@
         <v>61</v>
       </c>
       <c r="B26">
-        <v>97.59919130654536</v>
+        <v>97.599191306545364</v>
       </c>
       <c r="C26">
         <v>164</v>
@@ -3615,25 +3638,25 @@
         <v>1.88</v>
       </c>
       <c r="F26">
-        <v>-0.2968887763567598</v>
+        <v>-0.29688877635675981</v>
       </c>
       <c r="G26">
         <v>1.8</v>
       </c>
       <c r="H26">
-        <v>-0.2712972325746177</v>
+        <v>-0.27129723257461769</v>
       </c>
       <c r="I26">
-        <v>28.28600044250488</v>
+        <v>28.286000442504879</v>
       </c>
       <c r="J26">
-        <v>28.64750022888184</v>
+        <v>28.647500228881839</v>
       </c>
       <c r="K26">
         <v>26.6414001083374</v>
       </c>
       <c r="L26">
-        <v>21.29690003395081</v>
+        <v>21.296900033950809</v>
       </c>
       <c r="M26">
         <v>0.99</v>
@@ -3678,7 +3701,7 @@
         <v>-171.36</v>
       </c>
       <c r="AB26">
-        <v>76.29000000000001</v>
+        <v>76.290000000000006</v>
       </c>
       <c r="AC26">
         <v>117.31</v>
@@ -3705,7 +3728,7 @@
         <v>143</v>
       </c>
       <c r="AK26">
-        <v>28.99857487224089</v>
+        <v>28.998574872240891</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3713,19 +3736,19 @@
         <v>62</v>
       </c>
       <c r="B27">
-        <v>96.05761940864291</v>
+        <v>96.057619408642907</v>
       </c>
       <c r="C27">
         <v>1985</v>
       </c>
       <c r="D27">
-        <v>158.17</v>
+        <v>158.16999999999999</v>
       </c>
       <c r="E27">
         <v>2.46</v>
       </c>
       <c r="F27">
-        <v>0.2079188498915419</v>
+        <v>0.20791884989154191</v>
       </c>
       <c r="G27">
         <v>1.87</v>
@@ -3734,22 +3757,22 @@
         <v>-0.1823704601906378</v>
       </c>
       <c r="I27">
-        <v>160.8040008544922</v>
+        <v>160.80400085449219</v>
       </c>
       <c r="J27">
-        <v>156.9764991760254</v>
+        <v>156.97649917602541</v>
       </c>
       <c r="K27">
         <v>145.496600189209</v>
       </c>
       <c r="L27">
-        <v>114.3312001419067</v>
+        <v>114.33120014190671</v>
       </c>
       <c r="M27">
         <v>1.02</v>
       </c>
       <c r="N27">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -3764,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -3823,7 +3846,7 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>97.49810462471569</v>
+        <v>97.498104624715694</v>
       </c>
       <c r="C28">
         <v>59</v>
@@ -3841,16 +3864,16 @@
         <v>2.44</v>
       </c>
       <c r="H28">
-        <v>0.5417475435074832</v>
+        <v>0.54174754350748322</v>
       </c>
       <c r="I28">
-        <v>14.72712497711182</v>
+        <v>14.727124977111821</v>
       </c>
       <c r="J28">
-        <v>14.22424998283386</v>
+        <v>14.224249982833861</v>
       </c>
       <c r="K28">
-        <v>12.84088748931885</v>
+        <v>12.840887489318851</v>
       </c>
       <c r="L28">
         <v>10.18423124074936</v>
@@ -3859,7 +3882,7 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3925,7 +3948,7 @@
         <v>145</v>
       </c>
       <c r="AK28">
-        <v>27.89677862409117</v>
+        <v>27.896778624091169</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3951,19 +3974,19 @@
         <v>2.54</v>
       </c>
       <c r="H29">
-        <v>0.6687857897703117</v>
+        <v>0.66878578977031167</v>
       </c>
       <c r="I29">
-        <v>44.29599990844726</v>
+        <v>44.295999908447257</v>
       </c>
       <c r="J29">
-        <v>42.9954999923706</v>
+        <v>42.995499992370597</v>
       </c>
       <c r="K29">
-        <v>37.82280014038086</v>
+        <v>37.822800140380863</v>
       </c>
       <c r="L29">
-        <v>33.35274998664856</v>
+        <v>33.352749986648561</v>
       </c>
       <c r="M29">
         <v>1.03</v>
@@ -4011,7 +4034,7 @@
         <v>81.48</v>
       </c>
       <c r="AC29">
-        <v>82.34999999999999</v>
+        <v>82.35</v>
       </c>
       <c r="AD29">
         <v>32.61</v>
@@ -4035,7 +4058,7 @@
         <v>146</v>
       </c>
       <c r="AK29">
-        <v>27.83872947079036</v>
+        <v>27.838729470790359</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4043,7 +4066,7 @@
         <v>65</v>
       </c>
       <c r="B30">
-        <v>98.23098306798079</v>
+        <v>98.230983067980787</v>
       </c>
       <c r="C30">
         <v>811</v>
@@ -4061,19 +4084,19 @@
         <v>2.4</v>
       </c>
       <c r="H30">
-        <v>0.4909322450023519</v>
+        <v>0.49093224500235189</v>
       </c>
       <c r="I30">
-        <v>259.9940063476562</v>
+        <v>259.99400634765618</v>
       </c>
       <c r="J30">
-        <v>253.5470024108887</v>
+        <v>253.54700241088869</v>
       </c>
       <c r="K30">
         <v>220.7918008422852</v>
       </c>
       <c r="L30">
-        <v>162.4278505706787</v>
+        <v>162.42785057067869</v>
       </c>
       <c r="M30">
         <v>1.03</v>
@@ -4109,7 +4132,7 @@
         <v>88.56</v>
       </c>
       <c r="Y30">
-        <v>266.41</v>
+        <v>266.41000000000003</v>
       </c>
       <c r="Z30">
         <v>15.23</v>
@@ -4130,7 +4153,7 @@
         <v>19.77</v>
       </c>
       <c r="AF30">
-        <v>-1.15</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="AG30">
         <v>45</v>
@@ -4145,7 +4168,7 @@
         <v>147</v>
       </c>
       <c r="AK30">
-        <v>26.85602302245975</v>
+        <v>26.856023022459748</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4153,7 +4176,7 @@
         <v>66</v>
       </c>
       <c r="B31">
-        <v>92.36795552185998</v>
+        <v>92.367955521859983</v>
       </c>
       <c r="C31">
         <v>1958</v>
@@ -4171,19 +4194,19 @@
         <v>1.66</v>
       </c>
       <c r="H31">
-        <v>-0.4491507773425774</v>
+        <v>-0.44915077734257741</v>
       </c>
       <c r="I31">
-        <v>52.01399993896484</v>
+        <v>52.013999938964837</v>
       </c>
       <c r="J31">
-        <v>50.85199966430664</v>
+        <v>50.851999664306639</v>
       </c>
       <c r="K31">
-        <v>51.17139991760254</v>
+        <v>51.171399917602542</v>
       </c>
       <c r="L31">
-        <v>43.9568000793457</v>
+        <v>43.956800079345697</v>
       </c>
       <c r="M31">
         <v>1.02</v>
@@ -4255,7 +4278,7 @@
         <v>148</v>
       </c>
       <c r="AK31">
-        <v>25.58456895401868</v>
+        <v>25.584568954018678</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4275,22 +4298,22 @@
         <v>1.18</v>
       </c>
       <c r="F32">
-        <v>-0.9061393597598822</v>
+        <v>-0.90613935975988225</v>
       </c>
       <c r="G32">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="H32">
-        <v>0.02089073382988708</v>
+        <v>2.0890733829887081E-2</v>
       </c>
       <c r="I32">
-        <v>55.29000091552734</v>
+        <v>55.290000915527337</v>
       </c>
       <c r="J32">
-        <v>54.49200038909912</v>
+        <v>54.492000389099118</v>
       </c>
       <c r="K32">
-        <v>51.59440002441406</v>
+        <v>51.594400024414057</v>
       </c>
       <c r="L32">
         <v>44.61344997406006</v>
@@ -4365,7 +4388,7 @@
         <v>149</v>
       </c>
       <c r="AK32">
-        <v>24.44508421944254</v>
+        <v>24.445084219442538</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4373,7 +4396,7 @@
         <v>68</v>
       </c>
       <c r="B33">
-        <v>99.29239322719232</v>
+        <v>99.292393227192321</v>
       </c>
       <c r="C33">
         <v>1138</v>
@@ -4391,16 +4414,16 @@
         <v>2.13</v>
       </c>
       <c r="H33">
-        <v>0.1479289800927155</v>
+        <v>0.14792898009271549</v>
       </c>
       <c r="I33">
-        <v>51.94000091552734</v>
+        <v>51.940000915527342</v>
       </c>
       <c r="J33">
         <v>49.89250030517578</v>
       </c>
       <c r="K33">
-        <v>47.11259986877442</v>
+        <v>47.112599868774417</v>
       </c>
       <c r="L33">
         <v>32.13994998931885</v>
@@ -4409,7 +4432,7 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4424,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U33" t="b">
         <v>0</v>
@@ -4442,13 +4465,13 @@
         <v>53.6</v>
       </c>
       <c r="Z33">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="AA33">
         <v>109.38</v>
       </c>
       <c r="AB33">
-        <v>37.05</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="AC33">
         <v>47.62</v>
@@ -4483,43 +4506,43 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>90.97801364670205</v>
+        <v>90.978013646702053</v>
       </c>
       <c r="C34">
         <v>864</v>
       </c>
       <c r="D34">
-        <v>98.54000000000001</v>
+        <v>98.54</v>
       </c>
       <c r="E34">
         <v>1.79</v>
       </c>
       <c r="F34">
-        <v>-0.3752209942228754</v>
+        <v>-0.37522099422287541</v>
       </c>
       <c r="G34">
         <v>1.32</v>
       </c>
       <c r="H34">
-        <v>-0.8810808146361934</v>
+        <v>-0.88108081463619337</v>
       </c>
       <c r="I34">
-        <v>96.41799926757812</v>
+        <v>96.417999267578125</v>
       </c>
       <c r="J34">
-        <v>93.37099952697754</v>
+        <v>93.370999526977542</v>
       </c>
       <c r="K34">
-        <v>87.80259979248046</v>
+        <v>87.802599792480464</v>
       </c>
       <c r="L34">
-        <v>72.38210006713867</v>
+        <v>72.382100067138666</v>
       </c>
       <c r="M34">
         <v>1.03</v>
       </c>
       <c r="N34">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -4549,7 +4572,7 @@
         <v>55.83</v>
       </c>
       <c r="Y34">
-        <v>99.40000000000001</v>
+        <v>99.4</v>
       </c>
       <c r="Z34">
         <v>10.79</v>
@@ -4558,13 +4581,13 @@
         <v>9.75</v>
       </c>
       <c r="AB34">
-        <v>18.67</v>
+        <v>18.670000000000002</v>
       </c>
       <c r="AC34">
         <v>110.39</v>
       </c>
       <c r="AD34">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="AE34">
         <v>37.29</v>
@@ -4593,7 +4616,7 @@
         <v>70</v>
       </c>
       <c r="B35">
-        <v>90.85165529441495</v>
+        <v>90.851655294414954</v>
       </c>
       <c r="C35">
         <v>1068</v>
@@ -4605,7 +4628,7 @@
         <v>1.81</v>
       </c>
       <c r="F35">
-        <v>-0.3578138346970718</v>
+        <v>-0.35781383469707179</v>
       </c>
       <c r="G35">
         <v>3.66</v>
@@ -4614,16 +4637,16 @@
         <v>2.091614147913988</v>
       </c>
       <c r="I35">
-        <v>28.80700035095215</v>
+        <v>28.807000350952151</v>
       </c>
       <c r="J35">
-        <v>27.2443751335144</v>
+        <v>27.244375133514399</v>
       </c>
       <c r="K35">
-        <v>24.31580009460449</v>
+        <v>24.315800094604491</v>
       </c>
       <c r="L35">
-        <v>19.35837500572205</v>
+        <v>19.358375005722049</v>
       </c>
       <c r="M35">
         <v>1.06</v>
@@ -4671,7 +4694,7 @@
         <v>-919.26</v>
       </c>
       <c r="AB35">
-        <v>17.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="AC35">
         <v>54.55</v>
@@ -4698,7 +4721,7 @@
         <v>151</v>
       </c>
       <c r="AK35">
-        <v>21.91327108358333</v>
+        <v>21.913271083583329</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4706,7 +4729,7 @@
         <v>71</v>
       </c>
       <c r="B36">
-        <v>92.57012888551934</v>
+        <v>92.570128885519338</v>
       </c>
       <c r="C36">
         <v>789</v>
@@ -4718,16 +4741,16 @@
         <v>1.5</v>
       </c>
       <c r="F36">
-        <v>-0.6276248073470262</v>
+        <v>-0.62762480734702619</v>
       </c>
       <c r="G36">
         <v>1.28</v>
       </c>
       <c r="H36">
-        <v>-0.9318961131413248</v>
+        <v>-0.93189611314132481</v>
       </c>
       <c r="I36">
-        <v>220.4027221679688</v>
+        <v>220.40272216796879</v>
       </c>
       <c r="J36">
         <v>208.5899787902832</v>
@@ -4736,13 +4759,13 @@
         <v>203.113034362793</v>
       </c>
       <c r="L36">
-        <v>182.3569067382813</v>
+        <v>182.35690673828131</v>
       </c>
       <c r="M36">
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4808,7 +4831,7 @@
         <v>152</v>
       </c>
       <c r="AK36">
-        <v>21.89580399295289</v>
+        <v>21.895803992952889</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -4816,7 +4839,7 @@
         <v>72</v>
       </c>
       <c r="B37">
-        <v>94.64240586302755</v>
+        <v>94.642405863027548</v>
       </c>
       <c r="C37">
         <v>2048</v>
@@ -4828,25 +4851,25 @@
         <v>2.48</v>
       </c>
       <c r="F37">
-        <v>0.2253260094173453</v>
+        <v>0.22532600941734529</v>
       </c>
       <c r="G37">
         <v>1.99</v>
       </c>
       <c r="H37">
-        <v>-0.02992456467524399</v>
+        <v>-2.992456467524399E-2</v>
       </c>
       <c r="I37">
-        <v>35.03800125122071</v>
+        <v>35.038001251220713</v>
       </c>
       <c r="J37">
-        <v>33.81350059509278</v>
+        <v>33.813500595092783</v>
       </c>
       <c r="K37">
         <v>32.61120029449463</v>
       </c>
       <c r="L37">
-        <v>27.43965006828308</v>
+        <v>27.439650068283079</v>
       </c>
       <c r="M37">
         <v>1.04</v>
@@ -4891,7 +4914,7 @@
         <v>3.31</v>
       </c>
       <c r="AB37">
-        <v>16.69</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="AC37">
         <v>111.24</v>
@@ -4918,7 +4941,7 @@
         <v>153</v>
       </c>
       <c r="AK37">
-        <v>21.8756756656231</v>
+        <v>21.875675665623099</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -4926,7 +4949,7 @@
         <v>73</v>
       </c>
       <c r="B38">
-        <v>90.16932019206469</v>
+        <v>90.169320192064689</v>
       </c>
       <c r="C38">
         <v>726</v>
@@ -4944,19 +4967,19 @@
         <v>3.7</v>
       </c>
       <c r="H38">
-        <v>2.14242944641912</v>
+        <v>2.1424294464191198</v>
       </c>
       <c r="I38">
-        <v>18.64799995422363</v>
+        <v>18.647999954223629</v>
       </c>
       <c r="J38">
         <v>18.33450012207031</v>
       </c>
       <c r="K38">
-        <v>17.72240001678467</v>
+        <v>17.722400016784668</v>
       </c>
       <c r="L38">
-        <v>14.39739999294281</v>
+        <v>14.397399992942811</v>
       </c>
       <c r="M38">
         <v>1.02</v>
@@ -4977,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U38" t="b">
         <v>0</v>
@@ -4995,7 +5018,7 @@
         <v>19.37</v>
       </c>
       <c r="Z38">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AA38">
         <v>32.19</v>
@@ -5028,7 +5051,7 @@
         <v>124</v>
       </c>
       <c r="AK38">
-        <v>21.15699753502065</v>
+        <v>21.156997535020651</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -5036,7 +5059,7 @@
         <v>74</v>
       </c>
       <c r="B39">
-        <v>95.24892595400556</v>
+        <v>95.248925954005557</v>
       </c>
       <c r="C39">
         <v>2111</v>
@@ -5048,13 +5071,13 @@
         <v>3.95</v>
       </c>
       <c r="F39">
-        <v>1.504752234563903</v>
+        <v>1.5047522345639031</v>
       </c>
       <c r="G39">
         <v>2.62</v>
       </c>
       <c r="H39">
-        <v>0.7704163867805743</v>
+        <v>0.77041638678057434</v>
       </c>
       <c r="I39">
         <v>126.2880004882813</v>
@@ -5066,7 +5089,7 @@
         <v>105.1284002685547</v>
       </c>
       <c r="L39">
-        <v>91.58795001983643</v>
+        <v>91.587950019836427</v>
       </c>
       <c r="M39">
         <v>1.06</v>
@@ -5087,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>3.888888888888889</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="U39" t="b">
         <v>0</v>
@@ -5102,7 +5125,7 @@
         <v>60.02</v>
       </c>
       <c r="Y39">
-        <v>130.05</v>
+        <v>130.05000000000001</v>
       </c>
       <c r="Z39">
         <v>2.09</v>
@@ -5158,25 +5181,25 @@
         <v>1.82</v>
       </c>
       <c r="F40">
-        <v>-0.3491102549341701</v>
+        <v>-0.34911025493417008</v>
       </c>
       <c r="G40">
         <v>1.63</v>
       </c>
       <c r="H40">
-        <v>-0.4872622512214259</v>
+        <v>-0.48726225122142591</v>
       </c>
       <c r="I40">
         <v>31.70999984741211</v>
       </c>
       <c r="J40">
-        <v>31.04199981689453</v>
+        <v>31.041999816894531</v>
       </c>
       <c r="K40">
-        <v>29.66479988098144</v>
+        <v>29.664799880981441</v>
       </c>
       <c r="L40">
-        <v>26.20374999046326</v>
+        <v>26.203749990463258</v>
       </c>
       <c r="M40">
         <v>1.02</v>
@@ -5212,7 +5235,7 @@
         <v>18.93</v>
       </c>
       <c r="Y40">
-        <v>32.59</v>
+        <v>32.590000000000003</v>
       </c>
       <c r="Z40">
         <v>6.69</v>
@@ -5227,7 +5250,7 @@
         <v>14.81</v>
       </c>
       <c r="AD40">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AE40">
         <v>-11.43</v>
@@ -5256,7 +5279,7 @@
         <v>76</v>
       </c>
       <c r="B41">
-        <v>97.1948445792267</v>
+        <v>97.194844579226697</v>
       </c>
       <c r="C41">
         <v>580</v>
@@ -5268,13 +5291,13 @@
         <v>6.64</v>
       </c>
       <c r="F41">
-        <v>3.846015190784473</v>
+        <v>3.8460151907844731</v>
       </c>
       <c r="G41">
         <v>4.32</v>
       </c>
       <c r="H41">
-        <v>2.930066573248655</v>
+        <v>2.9300665732486548</v>
       </c>
       <c r="I41">
         <v>106.4460006713867</v>
@@ -5283,16 +5306,16 @@
         <v>102.9455005645752</v>
       </c>
       <c r="K41">
-        <v>94.78079986572266</v>
+        <v>94.780799865722656</v>
       </c>
       <c r="L41">
-        <v>67.76014999389649</v>
+        <v>67.760149993896491</v>
       </c>
       <c r="M41">
         <v>1.03</v>
       </c>
       <c r="N41">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -5307,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U41" t="b">
         <v>0</v>
@@ -5331,7 +5354,7 @@
         <v>6.97</v>
       </c>
       <c r="AB41">
-        <v>18.85</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="AC41">
         <v>19.55</v>
@@ -5366,7 +5389,7 @@
         <v>77</v>
       </c>
       <c r="B42">
-        <v>92.67121556734899</v>
+        <v>92.671215567348995</v>
       </c>
       <c r="C42">
         <v>321</v>
@@ -5381,22 +5404,22 @@
         <v>-1.071507375255015</v>
       </c>
       <c r="G42">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H42">
-        <v>-1.363826150434941</v>
+        <v>-1.3638261504349409</v>
       </c>
       <c r="I42">
-        <v>270.2099914550781</v>
+        <v>270.20999145507812</v>
       </c>
       <c r="J42">
-        <v>265.3885009765625</v>
+        <v>265.38850097656251</v>
       </c>
       <c r="K42">
-        <v>261.3424017333984</v>
+        <v>261.34240173339839</v>
       </c>
       <c r="L42">
-        <v>216.546100692749</v>
+        <v>216.54610069274901</v>
       </c>
       <c r="M42">
         <v>1.02</v>
@@ -5429,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>150.02</v>
+        <v>150.02000000000001</v>
       </c>
       <c r="Y42">
         <v>278.73</v>
@@ -5438,16 +5461,16 @@
         <v>154.13</v>
       </c>
       <c r="AA42">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AB42">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="AC42">
-        <v>8.210000000000001</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="AD42">
-        <v>158.08</v>
+        <v>158.08000000000001</v>
       </c>
       <c r="AE42">
         <v>4.12</v>
@@ -5456,7 +5479,7 @@
         <v>13.23</v>
       </c>
       <c r="AG42">
-        <v>-8.210000000000001</v>
+        <v>-8.2100000000000009</v>
       </c>
       <c r="AH42" t="s">
         <v>109</v>
@@ -5476,13 +5499,13 @@
         <v>78</v>
       </c>
       <c r="B43">
-        <v>90.80111195350013</v>
+        <v>90.801111953500126</v>
       </c>
       <c r="C43">
         <v>1449</v>
       </c>
       <c r="D43">
-        <v>128.95</v>
+        <v>128.94999999999999</v>
       </c>
       <c r="E43">
         <v>0.92</v>
@@ -5494,19 +5517,19 @@
         <v>1.28</v>
       </c>
       <c r="H43">
-        <v>-0.9318961131413248</v>
+        <v>-0.93189611314132481</v>
       </c>
       <c r="I43">
-        <v>128.6960006713867</v>
+        <v>128.69600067138671</v>
       </c>
       <c r="J43">
-        <v>127.0529998779297</v>
+        <v>127.05299987792969</v>
       </c>
       <c r="K43">
         <v>122.7791998291016</v>
       </c>
       <c r="L43">
-        <v>108.2472498703003</v>
+        <v>108.24724987030029</v>
       </c>
       <c r="M43">
         <v>1.01</v>
@@ -5527,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U43" t="b">
         <v>1</v>
@@ -5551,7 +5574,7 @@
         <v>19.48</v>
       </c>
       <c r="AB43">
-        <v>2.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="AC43">
         <v>28.77</v>
@@ -5560,7 +5583,7 @@
         <v>23.63</v>
       </c>
       <c r="AE43">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="AF43">
         <v>12.5</v>
@@ -5578,7 +5601,7 @@
         <v>149</v>
       </c>
       <c r="AK43">
-        <v>10.45081432260853</v>
+        <v>10.450814322608529</v>
       </c>
     </row>
     <row r="44" spans="1:37">
@@ -5586,7 +5609,7 @@
         <v>79</v>
       </c>
       <c r="B44">
-        <v>92.97447561283801</v>
+        <v>92.974475612838006</v>
       </c>
       <c r="C44">
         <v>374</v>
@@ -5598,16 +5621,16 @@
         <v>1.44</v>
       </c>
       <c r="F44">
-        <v>-0.6798462859244366</v>
+        <v>-0.67984628592443663</v>
       </c>
       <c r="G44">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H44">
-        <v>0.07170603233501845</v>
+        <v>7.1706032335018446E-2</v>
       </c>
       <c r="I44">
-        <v>181.6480010986328</v>
+        <v>181.64800109863279</v>
       </c>
       <c r="J44">
         <v>182.0780014038086</v>
@@ -5664,7 +5687,7 @@
         <v>15.77</v>
       </c>
       <c r="AC44">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="AD44">
         <v>5.14</v>
@@ -5688,7 +5711,7 @@
         <v>141</v>
       </c>
       <c r="AK44">
-        <v>9.34095517008392</v>
+        <v>9.3409551700839195</v>
       </c>
     </row>
     <row r="45" spans="1:37">
@@ -5696,7 +5719,7 @@
         <v>80</v>
       </c>
       <c r="B45">
-        <v>96.25979277230225</v>
+        <v>96.259792772302248</v>
       </c>
       <c r="C45">
         <v>2891</v>
@@ -5705,16 +5728,16 @@
         <v>3480</v>
       </c>
       <c r="E45">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="F45">
-        <v>-1.115025274069524</v>
+        <v>-1.1150252740695239</v>
       </c>
       <c r="G45">
         <v>1.49</v>
       </c>
       <c r="H45">
-        <v>-0.6651157959893854</v>
+        <v>-0.66511579598938542</v>
       </c>
       <c r="I45">
         <v>3444.885986328125</v>
@@ -5723,7 +5746,7 @@
         <v>3340.057983398438</v>
       </c>
       <c r="K45">
-        <v>3139.489594726563</v>
+        <v>3139.4895947265632</v>
       </c>
       <c r="L45">
         <v>2554.674146728516</v>
@@ -5732,7 +5755,7 @@
         <v>1.03</v>
       </c>
       <c r="N45">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -5780,7 +5803,7 @@
         <v>9.82</v>
       </c>
       <c r="AE45">
-        <v>9.630000000000001</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="AF45">
         <v>42.04</v>
@@ -5798,7 +5821,7 @@
         <v>132</v>
       </c>
       <c r="AK45">
-        <v>5.821711690395653</v>
+        <v>5.8217116903956532</v>
       </c>
     </row>
     <row r="46" spans="1:37">
@@ -5806,19 +5829,19 @@
         <v>81</v>
       </c>
       <c r="B46">
-        <v>90.06823351023503</v>
+        <v>90.068233510235032</v>
       </c>
       <c r="C46">
         <v>1984</v>
       </c>
       <c r="D46">
-        <v>132.98</v>
+        <v>132.97999999999999</v>
       </c>
       <c r="E46">
         <v>1.37</v>
       </c>
       <c r="F46">
-        <v>-0.7407713442647488</v>
+        <v>-0.74077134426474878</v>
       </c>
       <c r="G46">
         <v>1.31</v>
@@ -5827,13 +5850,13 @@
         <v>-0.8937846392624762</v>
       </c>
       <c r="I46">
-        <v>133.7819976806641</v>
+        <v>133.78199768066409</v>
       </c>
       <c r="J46">
-        <v>135.3624984741211</v>
+        <v>135.36249847412111</v>
       </c>
       <c r="K46">
-        <v>130.2101995849609</v>
+        <v>130.21019958496089</v>
       </c>
       <c r="L46">
         <v>114.8634000396729</v>
@@ -5857,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="T46">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U46" t="b">
         <v>1</v>
@@ -5869,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="X46">
-        <v>79.79000000000001</v>
+        <v>79.790000000000006</v>
       </c>
       <c r="Y46">
         <v>143.53</v>
@@ -5878,7 +5901,7 @@
         <v>3.45</v>
       </c>
       <c r="AA46">
-        <v>317.72</v>
+        <v>317.72000000000003</v>
       </c>
       <c r="AB46">
         <v>1.28</v>
@@ -5908,10 +5931,11 @@
         <v>123</v>
       </c>
       <c r="AK46">
-        <v>5.815744262003619</v>
+        <v>5.8157442620036193</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>